--- a/exports/trend_1d/ITC_full_report.xlsx
+++ b/exports/trend_1d/ITC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7.6</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H2" t="n">
-        <v>216.45</v>
+        <v>188.7</v>
       </c>
       <c r="I2" t="n">
         <v>202.4658415542288</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K2" t="n">
-        <v>10.01</v>
+        <v>-4.09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.54</v>
+        <v>4.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.17</v>
+        <v>9.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.97</v>
+        <v>12.82</v>
       </c>
       <c r="O2" t="n">
         <v>2.88</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.2</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42101</v>
+        <v>42102</v>
       </c>
       <c r="H3" t="n">
-        <v>187.25</v>
+        <v>190.35</v>
       </c>
       <c r="I3" t="n">
         <v>189.2683528969443</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" t="n">
-        <v>0.77</v>
+        <v>-0.87</v>
       </c>
       <c r="L3" t="n">
         <v>4.32</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>7.63</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42122</v>
+        <v>42123</v>
       </c>
       <c r="H4" t="n">
-        <v>185.6</v>
+        <v>180.4</v>
       </c>
       <c r="I4" t="n">
         <v>182.7620453983822</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.5</v>
+        <v>-5.23</v>
       </c>
       <c r="L4" t="n">
-        <v>3.65</v>
+        <v>5.46</v>
       </c>
       <c r="M4" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
       <c r="N4" t="n">
         <v>2.84</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42201</v>
+        <v>42202</v>
       </c>
       <c r="H5" t="n">
-        <v>174.85</v>
+        <v>177.2</v>
       </c>
       <c r="I5" t="n">
         <v>176.2144220138138</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K5" t="n">
-        <v>3.08</v>
+        <v>1.77</v>
       </c>
       <c r="L5" t="n">
         <v>2.38</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42306</v>
+        <v>42307</v>
       </c>
       <c r="H6" t="n">
-        <v>192.4</v>
+        <v>184</v>
       </c>
       <c r="I6" t="n">
         <v>185.5418479506327</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" t="n">
-        <v>8.58</v>
+        <v>3.84</v>
       </c>
       <c r="L6" t="n">
         <v>6.91</v>
@@ -783,7 +854,7 @@
         <v>2.94</v>
       </c>
       <c r="N6" t="n">
-        <v>3.19</v>
+        <v>4.37</v>
       </c>
       <c r="O6" t="n">
         <v>1.34</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>9.09</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42429</v>
+        <v>42430</v>
       </c>
       <c r="H7" t="n">
-        <v>162.5</v>
+        <v>178.9</v>
       </c>
       <c r="I7" t="n">
         <v>171.2094307851847</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K7" t="n">
-        <v>11.68</v>
+        <v>2.77</v>
       </c>
       <c r="L7" t="n">
         <v>5.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.47</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.17</v>
+        <v>10.09</v>
       </c>
       <c r="O7" t="n">
         <v>-4.37</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>14.51</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42636</v>
+        <v>42639</v>
       </c>
       <c r="H8" t="n">
-        <v>209</v>
+        <v>204.6</v>
       </c>
       <c r="I8" t="n">
         <v>207.7334201097443</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K8" t="n">
-        <v>16.83</v>
+        <v>14.37</v>
       </c>
       <c r="L8" t="n">
         <v>6.26</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>6.85</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42678</v>
+        <v>42681</v>
       </c>
       <c r="H9" t="n">
-        <v>205.4</v>
+        <v>211.55</v>
       </c>
       <c r="I9" t="n">
         <v>207.3016611856523</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.39</v>
+        <v>-3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>3.35</v>
+        <v>4.64</v>
       </c>
       <c r="M9" t="n">
         <v>4.64</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>9.09</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42689</v>
+        <v>42690</v>
       </c>
       <c r="H10" t="n">
-        <v>195.85</v>
+        <v>190.4</v>
       </c>
       <c r="I10" t="n">
         <v>193.9355375960935</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.42</v>
+        <v>-10</v>
       </c>
       <c r="L10" t="n">
-        <v>8.08</v>
+        <v>11.08</v>
       </c>
       <c r="M10" t="n">
         <v>6.41</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>12.15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42733</v>
+        <v>42734</v>
       </c>
       <c r="H11" t="n">
-        <v>194.6</v>
+        <v>199.25</v>
       </c>
       <c r="I11" t="n">
         <v>196.5974353413383</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.21</v>
+        <v>-4.65</v>
       </c>
       <c r="L11" t="n">
-        <v>3.78</v>
+        <v>4.99</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.51</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42796</v>
+        <v>42797</v>
       </c>
       <c r="H12" t="n">
-        <v>218.35</v>
+        <v>215.65</v>
       </c>
       <c r="I12" t="n">
         <v>215.8822614633874</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K12" t="n">
-        <v>9.59</v>
+        <v>8.23</v>
       </c>
       <c r="L12" t="n">
         <v>2.18</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>6.91</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42810</v>
+        <v>42811</v>
       </c>
       <c r="H13" t="n">
-        <v>221.4</v>
+        <v>231.95</v>
       </c>
       <c r="I13" t="n">
         <v>229.9352794417552</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.67</v>
+        <v>-7.56</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9</v>
+        <v>10.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>3.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.38</v>
+        <v>4.77</v>
       </c>
       <c r="O13" t="n">
         <v>-1.24</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>6.58</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42933</v>
+        <v>42934</v>
       </c>
       <c r="H14" t="n">
-        <v>268.15</v>
+        <v>234.65</v>
       </c>
       <c r="I14" t="n">
         <v>264.4551529668748</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K14" t="n">
-        <v>15.61</v>
+        <v>1.16</v>
       </c>
       <c r="L14" t="n">
         <v>3.69</v>
       </c>
       <c r="M14" t="n">
-        <v>1.65</v>
+        <v>9.99</v>
       </c>
       <c r="N14" t="n">
-        <v>3.56</v>
+        <v>12.49</v>
       </c>
       <c r="O14" t="n">
         <v>4.77</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>14.91</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43077</v>
+        <v>43080</v>
       </c>
       <c r="H15" t="n">
-        <v>216.25</v>
+        <v>219.55</v>
       </c>
       <c r="I15" t="n">
         <v>216.8591326994874</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K15" t="n">
-        <v>7.84</v>
+        <v>6.44</v>
       </c>
       <c r="L15" t="n">
         <v>3.81</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.27</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43147</v>
+        <v>43150</v>
       </c>
       <c r="H16" t="n">
-        <v>219.7</v>
+        <v>217.75</v>
       </c>
       <c r="I16" t="n">
         <v>219.2894003594058</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="L16" t="n">
         <v>3.26</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.92</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43207</v>
+        <v>43208</v>
       </c>
       <c r="H17" t="n">
-        <v>220.7</v>
+        <v>227.05</v>
       </c>
       <c r="I17" t="n">
         <v>223.1302200925645</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.35</v>
+        <v>-4.27</v>
       </c>
       <c r="L17" t="n">
-        <v>3.01</v>
+        <v>5.63</v>
       </c>
       <c r="M17" t="n">
         <v>1.82</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.13</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43251</v>
+        <v>43252</v>
       </c>
       <c r="H18" t="n">
-        <v>224.05</v>
+        <v>222.65</v>
       </c>
       <c r="I18" t="n">
         <v>223.4891142868587</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.32</v>
+        <v>-1.94</v>
       </c>
       <c r="L18" t="n">
         <v>2.64</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.91</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43290</v>
+        <v>43291</v>
       </c>
       <c r="H19" t="n">
-        <v>226.35</v>
+        <v>228.5</v>
       </c>
       <c r="I19" t="n">
         <v>226.6857612425757</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.66</v>
+        <v>-2.63</v>
       </c>
       <c r="L19" t="n">
-        <v>2.22</v>
+        <v>2.76</v>
       </c>
       <c r="M19" t="n">
         <v>0.85</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>6.21</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43353</v>
+        <v>43354</v>
       </c>
       <c r="H20" t="n">
-        <v>252.8</v>
+        <v>245.05</v>
       </c>
       <c r="I20" t="n">
         <v>249.6881645491799</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K20" t="n">
-        <v>10.63</v>
+        <v>7.24</v>
       </c>
       <c r="L20" t="n">
         <v>3.92</v>
@@ -1581,7 +1820,7 @@
         <v>0.51</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>3.07</v>
       </c>
       <c r="O20" t="n">
         <v>0.95</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.72</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43473</v>
+        <v>43474</v>
       </c>
       <c r="H21" t="n">
-        <v>234.4</v>
+        <v>239.5</v>
       </c>
       <c r="I21" t="n">
         <v>236.4229861791225</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K21" t="n">
-        <v>4.35</v>
+        <v>2.26</v>
       </c>
       <c r="L21" t="n">
         <v>3.86</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>5.92</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43487</v>
+        <v>43488</v>
       </c>
       <c r="H22" t="n">
-        <v>238.95</v>
+        <v>228.7</v>
       </c>
       <c r="I22" t="n">
         <v>231.6250195954741</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.23</v>
+        <v>-4.51</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>5.32</v>
       </c>
       <c r="M22" t="n">
         <v>0.29</v>
       </c>
       <c r="N22" t="n">
-        <v>0.87</v>
+        <v>4.29</v>
       </c>
       <c r="O22" t="n">
         <v>2.18</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43530</v>
+        <v>43531</v>
       </c>
       <c r="H23" t="n">
-        <v>235.7</v>
+        <v>239.25</v>
       </c>
       <c r="I23" t="n">
         <v>239.1530867353221</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K23" t="n">
-        <v>-3.06</v>
+        <v>-4.61</v>
       </c>
       <c r="L23" t="n">
         <v>6.17</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>5.83</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H24" t="n">
-        <v>245.5</v>
+        <v>238.55</v>
       </c>
       <c r="I24" t="n">
         <v>241.2289684741823</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K24" t="n">
-        <v>2.61</v>
+        <v>-0.29</v>
       </c>
       <c r="L24" t="n">
         <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>0.64</v>
+        <v>0.88</v>
       </c>
       <c r="N24" t="n">
-        <v>1.66</v>
+        <v>2.83</v>
       </c>
       <c r="O24" t="n">
         <v>1.51</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H25" t="n">
-        <v>196.3</v>
+        <v>210.15</v>
       </c>
       <c r="I25" t="n">
         <v>207.588539908256</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K25" t="n">
-        <v>17.71</v>
+        <v>11.91</v>
       </c>
       <c r="L25" t="n">
         <v>7.17</v>
       </c>
       <c r="M25" t="n">
-        <v>1.98</v>
+        <v>5.04</v>
       </c>
       <c r="N25" t="n">
-        <v>2.72</v>
+        <v>7.06</v>
       </c>
       <c r="O25" t="n">
         <v>-2.83</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.48</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43789</v>
+        <v>43790</v>
       </c>
       <c r="H26" t="n">
-        <v>206.75</v>
+        <v>202.65</v>
       </c>
       <c r="I26" t="n">
         <v>203.7369045588196</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.62</v>
+        <v>-3.57</v>
       </c>
       <c r="L26" t="n">
         <v>5.38</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.19</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H27" t="n">
-        <v>146.7</v>
+        <v>149.7</v>
       </c>
       <c r="I27" t="n">
         <v>148.0018617559721</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K27" t="n">
-        <v>27.61</v>
+        <v>26.13</v>
       </c>
       <c r="L27" t="n">
         <v>2.79</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>22.24</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43957</v>
+        <v>43958</v>
       </c>
       <c r="H28" t="n">
-        <v>135.15</v>
+        <v>132.8</v>
       </c>
       <c r="I28" t="n">
         <v>133.6079278396525</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K28" t="n">
-        <v>-9.720000000000001</v>
+        <v>-11.29</v>
       </c>
       <c r="L28" t="n">
         <v>11.59</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>15.34</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43971</v>
+        <v>43972</v>
       </c>
       <c r="H29" t="n">
-        <v>144.95</v>
+        <v>155.8</v>
       </c>
       <c r="I29" t="n">
         <v>150.5863216459672</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.15</v>
+        <v>-17.32</v>
       </c>
       <c r="L29" t="n">
-        <v>9.9</v>
+        <v>18.22</v>
       </c>
       <c r="M29" t="n">
         <v>5.03</v>
       </c>
       <c r="N29" t="n">
-        <v>4.13</v>
+        <v>7.49</v>
       </c>
       <c r="O29" t="n">
         <v>-1.74</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>16.43</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44074</v>
+        <v>44075</v>
       </c>
       <c r="H30" t="n">
-        <v>157.6</v>
+        <v>156.85</v>
       </c>
       <c r="I30" t="n">
         <v>157.0713585800209</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K30" t="n">
-        <v>1.16</v>
+        <v>0.67</v>
       </c>
       <c r="L30" t="n">
         <v>8.630000000000001</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>6.95</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44139</v>
+        <v>44140</v>
       </c>
       <c r="H31" t="n">
-        <v>140.05</v>
+        <v>144.1</v>
       </c>
       <c r="I31" t="n">
         <v>143.9245031004127</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K31" t="n">
-        <v>10.71</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>1.59</v>
@@ -2208,7 +2579,7 @@
         <v>1.66</v>
       </c>
       <c r="N31" t="n">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="O31" t="n">
         <v>-0.48</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.26</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44203</v>
+        <v>44204</v>
       </c>
       <c r="H32" t="n">
-        <v>167.25</v>
+        <v>166.15</v>
       </c>
       <c r="I32" t="n">
         <v>166.3188346179865</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K32" t="n">
-        <v>16.07</v>
+        <v>15.3</v>
       </c>
       <c r="L32" t="n">
         <v>2.57</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>8.44</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44211</v>
+        <v>44214</v>
       </c>
       <c r="H33" t="n">
-        <v>179.65</v>
+        <v>181.2</v>
       </c>
       <c r="I33" t="n">
         <v>180.1776586091472</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.130000000000001</v>
+        <v>-9.06</v>
       </c>
       <c r="L33" t="n">
-        <v>8.460000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="M33" t="n">
         <v>1.26</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>8.49</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H34" t="n">
-        <v>178.1</v>
+        <v>170.75</v>
       </c>
       <c r="I34" t="n">
         <v>174.1718040557672</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.71</v>
+        <v>-5.77</v>
       </c>
       <c r="L34" t="n">
         <v>8.17</v>
       </c>
       <c r="M34" t="n">
-        <v>0.63</v>
+        <v>1.82</v>
       </c>
       <c r="N34" t="n">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="O34" t="n">
         <v>0.86</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.54</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H35" t="n">
-        <v>173.65</v>
+        <v>179.5</v>
       </c>
       <c r="I35" t="n">
         <v>179.2355516844853</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.7</v>
+        <v>-5.12</v>
       </c>
       <c r="L35" t="n">
-        <v>3.31</v>
+        <v>5.83</v>
       </c>
       <c r="M35" t="n">
         <v>2.13</v>
       </c>
       <c r="N35" t="n">
-        <v>1.52</v>
+        <v>3.37</v>
       </c>
       <c r="O35" t="n">
         <v>-4.13</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.92</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44295</v>
+        <v>44298</v>
       </c>
       <c r="H36" t="n">
-        <v>175.7</v>
+        <v>169.3</v>
       </c>
       <c r="I36" t="n">
         <v>171.3319331022454</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.12</v>
+        <v>-5.68</v>
       </c>
       <c r="L36" t="n">
-        <v>3.96</v>
+        <v>5.82</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="N36" t="n">
-        <v>3.39</v>
+        <v>3.64</v>
       </c>
       <c r="O36" t="n">
         <v>3.37</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>9.18</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44328</v>
+        <v>44330</v>
       </c>
       <c r="H37" t="n">
-        <v>167.65</v>
+        <v>175.1</v>
       </c>
       <c r="I37" t="n">
         <v>174.325767256066</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K37" t="n">
-        <v>0.97</v>
+        <v>-3.43</v>
       </c>
       <c r="L37" t="n">
-        <v>2.78</v>
+        <v>3.84</v>
       </c>
       <c r="M37" t="n">
         <v>0.91</v>
       </c>
       <c r="N37" t="n">
-        <v>1.65</v>
+        <v>4.44</v>
       </c>
       <c r="O37" t="n">
         <v>-3.64</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.42</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44364</v>
+        <v>44365</v>
       </c>
       <c r="H38" t="n">
-        <v>169.6</v>
+        <v>168.65</v>
       </c>
       <c r="I38" t="n">
         <v>169.2742653674662</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.14</v>
+        <v>-3.68</v>
       </c>
       <c r="L38" t="n">
-        <v>3.91</v>
+        <v>4.63</v>
       </c>
       <c r="M38" t="n">
         <v>2.23</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>4.84</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44399</v>
+        <v>44400</v>
       </c>
       <c r="H39" t="n">
-        <v>170.7</v>
+        <v>175.2</v>
       </c>
       <c r="I39" t="n">
         <v>171.6653792845048</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.22</v>
+        <v>-3.88</v>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>4.45</v>
       </c>
       <c r="M39" t="n">
         <v>0.8</v>
       </c>
       <c r="N39" t="n">
-        <v>1.14</v>
+        <v>2.64</v>
       </c>
       <c r="O39" t="n">
         <v>-0.5600000000000001</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.57</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H40" t="n">
-        <v>201.8</v>
+        <v>195.15</v>
       </c>
       <c r="I40" t="n">
         <v>199.2101694434406</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="n">
-        <v>15.18</v>
+        <v>11.39</v>
       </c>
       <c r="L40" t="n">
         <v>3.82</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.2</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44592</v>
+        <v>44593</v>
       </c>
       <c r="H41" t="n">
-        <v>181.6</v>
+        <v>187.85</v>
       </c>
       <c r="I41" t="n">
         <v>185.937371866737</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K41" t="n">
-        <v>6.94</v>
+        <v>3.74</v>
       </c>
       <c r="L41" t="n">
         <v>3.89</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>8.119999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H42" t="n">
-        <v>191.7</v>
+        <v>180.95</v>
       </c>
       <c r="I42" t="n">
         <v>181.4261286394925</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K42" t="n">
-        <v>2.05</v>
+        <v>-3.67</v>
       </c>
       <c r="L42" t="n">
-        <v>3.78</v>
+        <v>4.07</v>
       </c>
       <c r="M42" t="n">
-        <v>0.63</v>
+        <v>2.79</v>
       </c>
       <c r="N42" t="n">
-        <v>1.76</v>
+        <v>5.61</v>
       </c>
       <c r="O42" t="n">
         <v>3.44</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>9.1</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44623</v>
+        <v>44624</v>
       </c>
       <c r="H43" t="n">
-        <v>180.9</v>
+        <v>186</v>
       </c>
       <c r="I43" t="n">
         <v>185.877214971391</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K43" t="n">
-        <v>0.03</v>
+        <v>-2.79</v>
       </c>
       <c r="L43" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="M43" t="n">
         <v>1.45</v>
       </c>
       <c r="N43" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="O43" t="n">
         <v>-5.61</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44831</v>
+        <v>44832</v>
       </c>
       <c r="H44" t="n">
-        <v>276.15</v>
+        <v>268</v>
       </c>
       <c r="I44" t="n">
         <v>271.2998593048789</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K44" t="n">
-        <v>48.47</v>
+        <v>44.09</v>
       </c>
       <c r="L44" t="n">
         <v>3.79</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>7.73</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44853</v>
+        <v>44854</v>
       </c>
       <c r="H45" t="n">
-        <v>285.6</v>
+        <v>288.4</v>
       </c>
       <c r="I45" t="n">
         <v>288.2518912045674</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.57</v>
+        <v>-7.61</v>
       </c>
       <c r="L45" t="n">
-        <v>6.92</v>
+        <v>7.99</v>
       </c>
       <c r="M45" t="n">
         <v>1.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>6.32</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44883</v>
+        <v>44886</v>
       </c>
       <c r="H46" t="n">
-        <v>281.25</v>
+        <v>278.05</v>
       </c>
       <c r="I46" t="n">
         <v>280.0528834743502</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.48</v>
+        <v>-3.59</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>4.39</v>
       </c>
       <c r="M46" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="N46" t="n">
         <v>2.55</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>5.67</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44951</v>
+        <v>44953</v>
       </c>
       <c r="H47" t="n">
-        <v>279.8</v>
+        <v>285.35</v>
       </c>
       <c r="I47" t="n">
         <v>285.1908950878633</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.63</v>
+        <v>-2.63</v>
       </c>
       <c r="L47" t="n">
-        <v>3.02</v>
+        <v>3.45</v>
       </c>
       <c r="M47" t="n">
-        <v>0.58</v>
+        <v>0.73</v>
       </c>
       <c r="N47" t="n">
         <v>2.43</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.01</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45131</v>
+        <v>45132</v>
       </c>
       <c r="H48" t="n">
-        <v>388.7</v>
+        <v>381.25</v>
       </c>
       <c r="I48" t="n">
         <v>385.0142048548067</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K48" t="n">
-        <v>36.22</v>
+        <v>33.61</v>
       </c>
       <c r="L48" t="n">
         <v>4.89</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>120</v>
+        <v>121</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45260</v>
+        <v>45261</v>
       </c>
       <c r="H49" t="n">
-        <v>359.35</v>
+        <v>370.95</v>
       </c>
       <c r="I49" t="n">
         <v>370.4186393191438</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K49" t="n">
-        <v>5.74</v>
+        <v>2.7</v>
       </c>
       <c r="L49" t="n">
         <v>2.78</v>
@@ -3234,7 +3821,7 @@
         <v>0.89</v>
       </c>
       <c r="N49" t="n">
-        <v>2.15</v>
+        <v>3.23</v>
       </c>
       <c r="O49" t="n">
         <v>-1.92</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.15</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45316</v>
+        <v>45320</v>
       </c>
       <c r="H50" t="n">
-        <v>375.75</v>
+        <v>370.95</v>
       </c>
       <c r="I50" t="n">
         <v>375.2528945582177</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="K50" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>2.76</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.96</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45372</v>
+        <v>45373</v>
       </c>
       <c r="H51" t="n">
-        <v>347.4</v>
+        <v>353.45</v>
       </c>
       <c r="I51" t="n">
         <v>352.6250783790925</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K51" t="n">
-        <v>6.35</v>
+        <v>4.72</v>
       </c>
       <c r="L51" t="n">
         <v>1.67</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>7.28</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H52" t="n">
-        <v>354.9</v>
+        <v>342.4</v>
       </c>
       <c r="I52" t="n">
         <v>345.504080173897</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K52" t="n">
-        <v>0.41</v>
+        <v>-3.13</v>
       </c>
       <c r="L52" t="n">
-        <v>2.94</v>
+        <v>6.01</v>
       </c>
       <c r="M52" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
         <v>3.6</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.53</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="H53" t="n">
-        <v>357.6</v>
+        <v>365.8</v>
       </c>
       <c r="I53" t="n">
         <v>364.7703342791322</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.44</v>
+        <v>-6.83</v>
       </c>
       <c r="L53" t="n">
-        <v>6.38</v>
+        <v>7.07</v>
       </c>
       <c r="M53" t="n">
         <v>1.64</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.45</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45573</v>
+        <v>45574</v>
       </c>
       <c r="H54" t="n">
-        <v>418.95</v>
+        <v>405.45</v>
       </c>
       <c r="I54" t="n">
         <v>413.2381844477899</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K54" t="n">
-        <v>14.53</v>
+        <v>10.84</v>
       </c>
       <c r="L54" t="n">
         <v>2.24</v>
@@ -3519,7 +4166,7 @@
         <v>1.86</v>
       </c>
       <c r="N54" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="O54" t="n">
         <v>2.29</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.67</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="H55" t="n">
-        <v>399.1</v>
+        <v>403.3</v>
       </c>
       <c r="I55" t="n">
         <v>399.7846832561762</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K55" t="n">
-        <v>1.57</v>
+        <v>0.53</v>
       </c>
       <c r="L55" t="n">
         <v>3.7</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.62</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H56" t="n">
-        <v>407.35</v>
+        <v>398.85</v>
       </c>
       <c r="I56" t="n">
         <v>405.1568058666936</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>-1.1</v>
       </c>
       <c r="L56" t="n">
         <v>1.88</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.58</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45756</v>
+        <v>45758</v>
       </c>
       <c r="H57" t="n">
-        <v>396.95</v>
+        <v>401.95</v>
       </c>
       <c r="I57" t="n">
         <v>398.999225698383</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K57" t="n">
-        <v>0.48</v>
+        <v>-0.78</v>
       </c>
       <c r="L57" t="n">
         <v>2.92</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.05</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H58" t="n">
-        <v>401.4</v>
+        <v>394.65</v>
       </c>
       <c r="I58" t="n">
         <v>396.1351864104739</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.14</v>
+        <v>-1.82</v>
       </c>
       <c r="L58" t="n">
         <v>2.04</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>5.31</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="H59" t="n">
-        <v>392.6</v>
+        <v>396.55</v>
       </c>
       <c r="I59" t="n">
         <v>394.2740976346668</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K59" t="n">
-        <v>0.52</v>
+        <v>-0.48</v>
       </c>
       <c r="L59" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="M59" t="n">
-        <v>0.89</v>
+        <v>2.97</v>
       </c>
       <c r="N59" t="n">
         <v>2.21</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>4</v>
+      </c>
+      <c r="U59" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>3.41</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="H60" t="n">
-        <v>384.45</v>
+        <v>382.35</v>
       </c>
       <c r="I60" t="n">
         <v>383.0190597285415</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K60" t="n">
-        <v>-3.05</v>
+        <v>-3.58</v>
       </c>
       <c r="L60" t="n">
-        <v>3.32</v>
+        <v>3.66</v>
       </c>
       <c r="M60" t="n">
         <v>0.18</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.16</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="H61" t="n">
-        <v>386.35</v>
+        <v>393</v>
       </c>
       <c r="I61" t="n">
         <v>392.878901393308</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.05</v>
+        <v>-2.79</v>
       </c>
       <c r="L61" t="n">
-        <v>1.74</v>
+        <v>3.2</v>
       </c>
       <c r="M61" t="n">
         <v>0.44</v>
       </c>
       <c r="N61" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="O61" t="n">
         <v>-0.55</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>4.32</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="H62" t="n">
-        <v>388.55</v>
+        <v>385.25</v>
       </c>
       <c r="I62" t="n">
         <v>386.937651120748</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.13</v>
+        <v>-1.97</v>
       </c>
       <c r="L62" t="n">
-        <v>1.68</v>
+        <v>2.19</v>
       </c>
       <c r="M62" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="N62" t="n">
         <v>1.52</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>4.9</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="H63" t="n">
-        <v>316.8</v>
+        <v>323.65</v>
       </c>
       <c r="I63" t="n">
         <v>318.3620753598644</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K63" t="n">
-        <v>17.77</v>
+        <v>15.99</v>
       </c>
       <c r="L63" t="n">
         <v>1.97</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>4</v>
+      </c>
+      <c r="U63" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>7.88</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H64" t="n">
-        <v>301.5</v>
+        <v>297.9</v>
       </c>
       <c r="I64" t="n">
         <v>298.3860093219051</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.84</v>
+        <v>-7.96</v>
       </c>
       <c r="L64" t="n">
-        <v>7.66</v>
+        <v>8.68</v>
       </c>
       <c r="M64" t="n">
         <v>2.11</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>5.7</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="H65" t="n">
-        <v>296.4</v>
+        <v>307.85</v>
       </c>
       <c r="I65" t="n">
         <v>302.8356116191056</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>-3.34</v>
       </c>
       <c r="L65" t="n">
-        <v>1.66</v>
+        <v>3.76</v>
       </c>
       <c r="M65" t="n">
         <v>1.89</v>
       </c>
       <c r="N65" t="n">
-        <v>2.27</v>
+        <v>3.86</v>
       </c>
       <c r="O65" t="n">
         <v>-1.19</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>7.07</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="H66" t="n">
-        <v>291.95</v>
+        <v>286.9</v>
       </c>
       <c r="I66" t="n">
         <v>290.5525462292044</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.16</v>
+        <v>-6.81</v>
       </c>
       <c r="L66" t="n">
-        <v>5.46</v>
+        <v>7.13</v>
       </c>
       <c r="M66" t="n">
         <v>0.7</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.1</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H67" t="n">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I67" t="n">
         <v>288.4111679898529</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.03</v>
+        <v>-0.73</v>
       </c>
       <c r="L67" t="n">
         <v>2.67</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>6.14</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="H68" t="n">
-        <v>273.05</v>
+        <v>270</v>
       </c>
       <c r="I68" t="n">
         <v>271.5182593667854</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K68" t="n">
-        <v>-5.52</v>
+        <v>-6.57</v>
       </c>
       <c r="L68" t="n">
-        <v>5.54</v>
+        <v>6.87</v>
       </c>
       <c r="M68" t="n">
         <v>0.52</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>49</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9335,7 +10170,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.6</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="6">
@@ -9345,7 +10180,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -9355,7 +10190,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8">
@@ -9365,7 +10200,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -9375,7 +10210,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -9385,7 +10220,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124.4</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="11">
@@ -9395,7 +10230,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -9405,7 +10240,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -9415,7 +10250,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.9</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="14">
@@ -9425,7 +10260,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.53</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -9435,7 +10270,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.59</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="16">
@@ -9445,7 +10280,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.44</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
@@ -9455,7 +10290,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48.47</v>
+        <v>44.09</v>
       </c>
     </row>
     <row r="18">
@@ -9465,7 +10300,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.7</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="19">
@@ -9475,7 +10310,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.05</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="20">
@@ -9485,7 +10320,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.35</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="21">
@@ -9495,7 +10330,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.59</v>
+        <v>18.22</v>
       </c>
     </row>
     <row r="22">
@@ -9505,7 +10340,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23">
@@ -9515,7 +10350,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -9525,7 +10360,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.69</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="25">
@@ -9535,7 +10370,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.59</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="26">
@@ -9545,7 +10380,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.04</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="27">
@@ -9555,7 +10390,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.43</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="28">
@@ -9565,7 +10400,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
